--- a/mapping/templates/GUIDE_Doppio/API_PDS002MI_ProductStructure.xlsx
+++ b/mapping/templates/GUIDE_Doppio/API_PDS002MI_ProductStructure.xlsx
@@ -162,56 +162,12 @@
     <author>System</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Company
-The field indicates company number, which is the primary identity in all files in the M3 system. The purpose of this is to be able to handle, in the same database, several companies completely or partially separated.
-A maximum of 999 companies may be handled in the same database.
-</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Facility
-The field indicates the facility used.
-Facilities are used to set authorization in time reporting component groups and for activities such as sales, production or distribution.
-A facility is a superior organizational level to a department but lower than a division, that is, a facility belongs to a division, which in turn belongs to a company. A facility can contain one or more warehouses. A user is always connected to a pre-selected facility. All product data and production data are stored per facility, and several facilities can exist in the same database. All planning occurs per warehouse, although the highest planning level in M3 can be the facility, when availability can be calculated per facility. However, this assumes that planning method 4 is used.
-Facilities are defined in (CRS008).
-</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Product
-The field indicates the product number.
-For a product structure with a product structure class type of 00-'Standard' (i.e. discrete items), the product number is the same as the item number manufactured (the output from the manufacturing order) and is always used together with structures to describe what a product consists of and how it is manufactured.
-There are scenarios where each process is created as a product number on (PDS001) to serve as a placeholder for product structure class types other than 00-'Standard'. In the cases where the product structure class type is Formula product structure, Routing product structure, Bulk item product structure, Packaging material product structure, or Packaged item product structure, the Product number field is used to identify a process required for the manufacture of the ultimate product number.
-</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Product structure type
-The field indicates a product structure type. You can define more than one product structure per product and facility.
-</t>
-      </text>
-    </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">Sequence number
 The field indicates the sequence number of a bill of material. This number is included in every key ID for material in a product structure or manufacturing order.
 The sequence number of a bill of material for a kit item may not be greater than 99.
 The number should contain 4 positions. It can be entered manually.
-</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Operation number
-The field indicates an operation number, which forms a unique ID for an operation when combined with a product number.
-For each operation number, enter the work center where the operation should be performed along with information such as operation name, run time and setup time.
-The operation number also indicates the order in which operations should be performed for a product.
-When an operation number has been entered on a material line in a product structure, it refers to the operation in which the material should first be used.
 </t>
       </text>
     </comment>
@@ -231,57 +187,6 @@
 </t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Used in standard
-Select the check box to enter standard code for each material and/or operation. The code controls whether materials and operations should be considered in estimate, requirements calculation and lead time calculation of the product, according to:
-Items that do not contain variants of materials or alternative operations normally have standard code 1 for all structure lines. Also items that contain variants of materials or operations normally have standard code 1 but combined with option percentage. Option percentage indicates how much of the materials and operations should be considered in estimate, requirements calculation and lead time calculation.
-For products with operations that are controlled by alternative routing (one 'standard' alternative routing must exists in PDS001) and record exists in PDS008, the operations will be included in the estimate, requirements and lead time calculation regardless of the option selected in this code. Otherwise, the option to include the operations in the calculation is still determined by this code.
-For products with operations that have record in PDS003, the operations will be included in the estimate, requirements and lead time calculation regardless of the option selected in this code. Otherwise, the option to include the operations in the calculation is still determined by this code.
-</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Selection ID - component
-The field indicates the ID of a selection matrix or a feature used to select an item for a component line instead of the item number. After an ID is entered, this field is controlled by the component selection type and the ID is validated based on the selection type specified. If you enter a feature, it must be defined with item number as an option (parameter type 2). If you enter a matrix, it must be an item number matrix (matrix type 3).
-</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>Selection type - component
-The field indicates selection type for a component.
-0: Validation takes place according to the search hierarchy in the parameters (function key F13).
-1: The entered identity is an item number.
-2: The entered identity is a matrix.
-3: The entered identity is a feature.</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Selection ID - quantity
-The field indicates a matrix, formula or feature to close the quantity for the BoM line instead of using the quantity.
-A formula is used to calculate the quantity used, while a selection matrix is used to select the quantity used.
-A feature is used to directly determine the quantity used via the option.
-What you specify here is controlled by the field for material selection type. The ID specified is validated according to the specified selection type.
-If you specify a feature, it must be defined with numeric options (parameter type 3 or 4).
-If you specify a matrix, it must be defined to give numeric replies (matrix type 1).
-If you specify a formula, you can also enter a result ID. If you leave the result ID blank, the last result of the formula is always selected.
-</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Selection type - quantity
-The field indicates a selection type for quantity.
-0: Validation is performed according to the search hirerchy in the parameters (function key F13).
-1: The entered value is a quantity.
-2: The entered identity is a matrix.
-3: The entered identity is a feature.
-4: The entered identity is a formula.</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -292,60 +197,6 @@
     <author>System</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Company
-The field indicates company number, which is the primary identity in all files in the M3 system. The purpose of this is to be able to handle, in the same database, several companies completely or partially separated.
-A maximum of 999 companies may be handled in the same database.
-</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Facility
-The field indicates the facility used.
-Facilities are used to set authorization in time reporting component groups and for activities such as sales, production or distribution.
-A facility is a superior organizational level to a department but lower than a division, that is, a facility belongs to a division, which in turn belongs to a company. A facility can contain one or more warehouses. A user is always connected to a pre-selected facility. All product data and production data are stored per facility, and several facilities can exist in the same database. All planning occurs per warehouse, although the highest planning level in M3 can be the facility, when availability can be calculated per facility. However, this assumes that planning method 4 is used.
-Facilities are defined in (CRS008).
-</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Product
-The field indicates the product number.
-For a product structure with a product structure class type of 00-'Standard' (i.e. discrete items), the product number is the same as the item number manufactured (the output from the manufacturing order) and is always used together with structures to describe what a product consists of and how it is manufactured.
-There are scenarios where each process is created as a product number on (PDS001) to serve as a placeholder for product structure class types other than 00-'Standard'. In the cases where the product structure class type is Formula product structure, Routing product structure, Bulk item product structure, Packaging material product structure, or Packaged item product structure, the Product number field is used to identify a process required for the manufacture of the ultimate product number.
-</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Product structure type
-The field indicates a product structure type. You can define more than one product structure per product and facility.
-</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Operation number
-The field indicates an operation number, which forms a unique ID for an operation when combined with a product number.
-For each operation number, enter the work center where the operation should be performed along with information such as operation name, run time and setup time.
-The operation number also indicates the order in which operations should be performed for a product.
-When an operation number has been entered on a material line in a product structure, it refers to the operation in which the material should first be used.
-</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Work center
-The field indicates a work center, which is a resource in which labor operations are performed.
-A work center can consist of one or more exchangeable machines or people. The work center can also be external and is then defined as a subcontract group.
-The work center is considered the smallest unit for capacity and load planning, unless M3 Scheduling Workbench (SWB) is active. In that case, planning is carried out for each work center resource.
-Work centers are defined in (PDS010).
-</t>
-      </text>
-    </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">Operation description
@@ -360,63 +211,6 @@
 The field indicates how many people are planned to perform an operation.
 This information forms the basis for calculating estimates, load and lead time. The standard value from the associated work center is proposed as default when entering new operations.
 </t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Phantom operation method
-The field indicates how this operation is processed if it is part of a phantom routing.
-1: Added as a new operation
-2: Accumulation of run time.</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Used in standard
-Select the check box to enter standard code for each material and/or operation. The code controls whether materials and operations should be considered in estimate, requirements calculation and lead time calculation of the product, according to:
-Items that do not contain variants of materials or alternative operations normally have standard code 1 for all structure lines. Also items that contain variants of materials or operations normally have standard code 1 but combined with option percentage. Option percentage indicates how much of the materials and operations should be considered in estimate, requirements calculation and lead time calculation.
-For products with operations that are controlled by alternative routing (one 'standard' alternative routing must exists in PDS001) and record exists in PDS008, the operations will be included in the estimate, requirements and lead time calculation regardless of the option selected in this code. Otherwise, the option to include the operations in the calculation is still determined by this code.
-For products with operations that have record in PDS003, the operations will be included in the estimate, requirements and lead time calculation regardless of the option selected in this code. Otherwise, the option to include the operations in the calculation is still determined by this code.
-</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Number of labor tickets
-The field indicates the number of labor tickets to be printed per operation. The number is determined per product record, per unique operation and by the labor ticket multiplier.
-The two values are multiplied to give the total number of labor tickets per operation.
-</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Multiplication factor - manufacturing
-The field indicates a multiplication factor used in product costing.
-The purpose of this factor is to neutralize any differences in unit for different products.
-</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Operation cost multiplier
-The field indicates the multiplier used during product costing.
-The multiplier can be used for either a volume-based or order-based cost driver.
-</t>
-      </text>
-    </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Automatic receipt
-Select the check box if (PMS050) for manufacturing orders or (MOS050) for work orders should be automatically displayed when reporting the last operation in an order.
-</t>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
-      <text>
-        <t>Time based production lot quantity
-The field indicates whether the production lot size entered is a fixed quantity or a time-related quantity.
-1: Quantity
-2: Hours.</t>
       </text>
     </comment>
   </commentList>
